--- a/测试用例-D9-用户列表排序参数.xlsx
+++ b/测试用例-D9-用户列表排序参数.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$3:$M$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$3:$K$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>缺陷：isAsc 未做枚举校验，非法值触发数据库异常并泄露 SQL 与服务器路径 ｜ 用例 22 条（通过 10 / 失败 12）</t>
+          <t>用例 22 条（通过 10 / 失败 12）</t>
         </is>
       </c>
     </row>
@@ -585,21 +585,11 @@
           <t>状态</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>关联缺陷</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-001</t>
+          <t>TC-001</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -653,17 +643,11 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>排序功能基准用例</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-002</t>
+          <t>TC-002</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -717,13 +701,11 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-003</t>
+          <t>TC-003</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -776,13 +758,11 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-004</t>
+          <t>TC-004</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -833,19 +813,13 @@
       <c r="K7" s="6" t="inlineStr">
         <is>
           <t>通过</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>逗号在字符白名单内</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-005</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -896,19 +870,13 @@
       <c r="K8" s="6" t="inlineStr">
         <is>
           <t>通过</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>空值不进入拼接逻辑</t>
         </is>
       </c>
     </row>
     <row r="9" ht="112" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-006</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -970,21 +938,11 @@
           <t>失败</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>核心缺陷用例，定级：高</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-007</t>
+          <t>TC-007</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1037,17 +995,11 @@
           <t>失败</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-008</t>
+          <t>TC-008</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1100,17 +1052,11 @@
           <t>失败</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-009</t>
+          <t>TC-009</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1161,23 +1107,13 @@
       <c r="K12" s="7" t="inlineStr">
         <is>
           <t>失败</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>limit 通过了字符白名单，但与分页追加的 LIMIT 冲突</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-010</t>
+          <t>TC-010</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1228,23 +1164,13 @@
       <c r="K13" s="7" t="inlineStr">
         <is>
           <t>失败</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>拼出的是语法非法语句，拿不到数据</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-011</t>
+          <t>TC-011</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1295,19 +1221,13 @@
       <c r="K14" s="6" t="inlineStr">
         <is>
           <t>通过</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>"=" 不在字符白名单内，被正确拦截</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-012</t>
+          <t>TC-012</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1358,19 +1278,13 @@
       <c r="K15" s="6" t="inlineStr">
         <is>
           <t>通过</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>"(" 不在字符白名单内，被正确拦截</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-013</t>
+          <t>TC-013</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1424,17 +1338,11 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>正向对照：同位置 orderByColumn 有校验，是 D9 预期依据的来源</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-014</t>
+          <t>TC-014</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1488,13 +1396,11 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="5" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-015</t>
+          <t>TC-015</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1549,21 +1455,11 @@
           <t>失败</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>新暴露点：字符白名单只拦特殊字符，不校验字段是否存在；与 D9 同属 SQL 异常信息泄露</t>
-        </is>
-      </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-016</t>
+          <t>TC-016</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1617,17 +1513,11 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>orderByColumn 为空时跳过排序拼接，isAsc 未参与，因此不触发泄露</t>
-        </is>
-      </c>
     </row>
     <row r="20" ht="44.5" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-017</t>
+          <t>TC-017</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1678,23 +1568,13 @@
       <c r="K20" s="7" t="inlineStr">
         <is>
           <t>失败</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>证明影响面为框架级</t>
         </is>
       </c>
     </row>
     <row r="21" ht="44.5" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-018</t>
+          <t>TC-018</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1747,17 +1627,11 @@
           <t>失败</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr"/>
     </row>
     <row r="22" ht="44.5" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-019</t>
+          <t>TC-019</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1810,17 +1684,11 @@
           <t>失败</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="44.5" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-020</t>
+          <t>TC-020</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1873,17 +1741,11 @@
           <t>失败</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="44.5" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-021</t>
+          <t>TC-021</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -1936,17 +1798,11 @@
           <t>失败</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="44.5" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-LIST-SORT-022</t>
+          <t>TC-022</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1999,18 +1855,12 @@
           <t>失败</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M25"/>
+  <autoFilter ref="A3:K25"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2022,7 +1872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2056,285 +1906,213 @@
     <row r="3" ht="17.5" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>关联缺陷</t>
+          <t>用例总数</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>D9 —— isAsc 未做枚举校验，非法值触发数据库异常并泄露 SQL 与服务器路径（定级：高）</t>
+          <t>22 条（通过 10 / 失败 12）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17.5" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>用例总数</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>22 条（通过 10 / 失败 12）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.5" customHeight="1">
-      <c r="A5" s="9" t="inlineStr"/>
-      <c r="B5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr"/>
+      <c r="B4" s="10" t="inlineStr"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>字段说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17.5" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>用例编号</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>TC-序号，同一文件内唯一</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17.5" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>用例编号</t>
+          <t>优先级</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>TC-模块-序号，同一文件内唯一</t>
+          <t>P0 核心必测 / P1 重要 / P2 一般</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17.5" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>优先级</t>
+          <t>用例类型</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>P0 核心必测 / P1 重要 / P2 一般</t>
+          <t>功能 / 边界 / 异常 / 安全 / 权限 / 组合 / 对照 / 回归</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17.5" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>用例类型</t>
+          <t>前置条件</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>功能 / 边界 / 异常 / 安全 / 权限 / 组合 / 回归</t>
+          <t>执行该用例前必须满足的状态</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17.5" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>前置条件</t>
+          <t>测试步骤</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>执行该用例前必须满足的状态</t>
+          <t>可被他人在相同环境照着重现的操作</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17.5" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>测试步骤</t>
+          <t>测试数据</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>可被他人在相同环境照着重现的操作</t>
+          <t>本条用例使用的具体参数值</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17.5" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>测试数据</t>
+          <t>预期结果</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>本条用例使用的具体参数值</t>
+          <t>执行之前写下的、功能正确时应有的表现</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17.5" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>预期结果</t>
+          <t>实际结果</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>执行之前写下的、功能正确时应有的表现</t>
+          <t>执行之后记录的真实响应</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17.5" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>实际结果</t>
+          <t>状态</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>执行之后记录的真实响应</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="17.5" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
           <t>通过 / 失败 / 待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>状态含义</t>
         </is>
       </c>
     </row>
     <row r="16" ht="17.5" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>关联缺陷</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>对应的缺陷编号，便于追溯</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>状态含义</t>
+          <t>实际结果与预期一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>预期结果未被满足，即接口行为不符合预期（不是用例写错了）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="17.5" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>待执行</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>实际结果与预期一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="17.5" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>预期结果未被满足，即接口行为不符合预期，已提交缺陷报告（不是用例写错了）</t>
+          <t>测试环境服务未启动，尚未执行，实际结果留空</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>执行情况</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17.5" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>待执行</t>
+          <t>执行状态</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>测试环境服务未启动，尚未执行，实际结果留空</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>执行情况</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="17.5" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>执行状态</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
           <t>全部 22 条用例已执行完毕，无未执行项。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="17.5" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="21" ht="17.5" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>证据</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>失败用例的截图见仓库 证据/ 目录，文件名以缺陷编号开头（如 D9-01-isAsc传xxx泄露SQL与服务器路径.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="17.5" customHeight="1">
-      <c r="A24" s="9" t="inlineStr"/>
-      <c r="B24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>能力边界</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="17.5" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>是否 SQL 注入</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>否。字符白名单挡住了 = ( ; 等构造注入所需的字符（TC-011 ~ TC-014 已验证被拦截），因此不能利用它窃取数据。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="31" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>但信息泄露成立</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>任意非法值都能触发数据库异常并泄露完整内部信息；TC-015 进一步表明，传一个不存在的列名同样会触发 SQL 异常并泄露，说明白名单只拦特殊字符、不校验字段是否存在。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="17.5" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>定级说明</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>按实际危害定级（信息泄露 / 高），不夸大为 SQL 注入，避免被开发反驳。</t>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>失败用例的截图见仓库 证据/ 目录（D9-01 ~ D9-04 共 4 张）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A17:B17"/>
+  <mergeCells count="3">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
